--- a/datos/clientes.xlsx
+++ b/datos/clientes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,40 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>['Lunes', 'Miércoles', 'Viernes']</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bruno lopez</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>45259810</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>['Lunes', 'Miércoles', 'Viernes']</t>
         </is>

--- a/datos/clientes.xlsx
+++ b/datos/clientes.xlsx
@@ -471,7 +471,7 @@
         <v>26218728</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -483,7 +483,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -505,11 +505,11 @@
         <v>45259810</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -517,7 +517,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
